--- a/artfynd/A 36208-2023 artfynd.xlsx
+++ b/artfynd/A 36208-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36208-2023 artfynd.xlsx
+++ b/artfynd/A 36208-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>91796635</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514795.5238033807</v>
+        <v>514796</v>
       </c>
       <c r="R2" t="n">
-        <v>7040969.309156247</v>
+        <v>7040969</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2017-08-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-08-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,37 +788,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91796644</v>
+        <v>91796636</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>4368</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -847,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514954.3004640888</v>
+        <v>514751</v>
       </c>
       <c r="R3" t="n">
-        <v>7041066.084318623</v>
+        <v>7041040</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,19 +860,9 @@
           <t>2017-08-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-08-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,12 +904,7 @@
         <v>91796647</v>
       </c>
       <c r="B4" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514783.4475832674</v>
+        <v>514783</v>
       </c>
       <c r="R4" t="n">
-        <v>7040969.253128476</v>
+        <v>7040969</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1008,19 +973,9 @@
           <t>2017-08-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-08-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,12 +1017,7 @@
         <v>91796646</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514771.7875827509</v>
+        <v>514772</v>
       </c>
       <c r="R5" t="n">
-        <v>7040975.899231288</v>
+        <v>7040976</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1136,19 +1086,9 @@
           <t>2017-08-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-08-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,6 +1120,119 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>91796644</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flakaflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>514954</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7041066</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-08-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-08-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 36208-2023 artfynd.xlsx
+++ b/artfynd/A 36208-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91796635</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91796636</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91796647</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91796646</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,8 +1262,20 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91796644</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>